--- a/glav_grups.xlsx
+++ b/glav_grups.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Семья\Documents\проекты\BookingMaster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410E4B2F-046D-40AB-BD24-D19D806324C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CC29DF-26F9-4FA4-B424-8378E210EBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8490" yWindow="450" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
